--- a/sample_data/ACL-Protocols-Summary.xlsx
+++ b/sample_data/ACL-Protocols-Summary.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{CC03F5E8-353A-9740-99E0-06FAF4DEB264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10512636-7D39-A74A-B50F-68588D96C7CA}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="8_{CC03F5E8-353A-9740-99E0-06FAF4DEB264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B4A5B8-D237-7C48-9CE0-6A23C4C854EC}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="-18980" windowWidth="28040" windowHeight="17440" xr2:uid="{AFA84863-E3FE-B041-9D6C-E0FD21125308}"/>
+    <workbookView xWindow="2520" yWindow="-18980" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{AFA84863-E3FE-B041-9D6C-E0FD21125308}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Moon" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="102">
   <si>
     <t>Melbourne</t>
   </si>
@@ -177,13 +178,178 @@
   </si>
   <si>
     <t>RTP Transition (12-24m)</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>Alternate</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>Knee Extensions</t>
+  </si>
+  <si>
+    <t>Extend surgical leg in front of you. Straighten leg as much as you can, allow gravity to gently continue to straighten your knee.</t>
+  </si>
+  <si>
+    <t>20-30minutes 3-4x per day</t>
+  </si>
+  <si>
+    <t>phase</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>exercise</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>prescription</t>
+  </si>
+  <si>
+    <t>Supine Knee Extensions</t>
+  </si>
+  <si>
+    <t>Prone Knee Extensions</t>
+  </si>
+  <si>
+    <t>Seated Knee Extensions</t>
+  </si>
+  <si>
+    <t>Heel Slides</t>
+  </si>
+  <si>
+    <t>Ankle Pumps</t>
+  </si>
+  <si>
+    <t>Lie on your back with your knee straight. Place a small towel roll under your heel and hold the position</t>
+  </si>
+  <si>
+    <t>Lie on your stomach with a small flat towel roll just above your knee.  Let your foot hang off the end of the bed.</t>
+  </si>
+  <si>
+    <t>Seated on a high bench, use your opposite leg to lift your surgical leg out as straight as possible while keeping the surgical leg relaxed.</t>
+  </si>
+  <si>
+    <t>Lie on your back with your knee bent and foot on the floor. Slide the foot to straighten the knee as much as possible, then return to start, always keeping the heel on the ground.</t>
+  </si>
+  <si>
+    <t>10-20reps 3-4x per day</t>
+  </si>
+  <si>
+    <t>10-20reps 2-3x per day</t>
+  </si>
+  <si>
+    <t>Sit with legs out straight with towel roll under your ankle. Flex and extend your foot at the ankle joint like you are pressing a gas pedal.</t>
+  </si>
+  <si>
+    <t>15reps every hour</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>goal</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>Quadriceps Set</t>
+  </si>
+  <si>
+    <t>Sit with your legs straight. Squeeze your quads to push the back of  your knee flat against the floor. Squeeze for 5s.</t>
+  </si>
+  <si>
+    <t>12reps 3x per day</t>
+  </si>
+  <si>
+    <t>Hamstring Set - Supine</t>
+  </si>
+  <si>
+    <t>Hamstring Set - Prone</t>
+  </si>
+  <si>
+    <t>Hamstring Set - Standing</t>
+  </si>
+  <si>
+    <t>Lie on your back and bend your knee roughly 90 degrees.  Push your heel down into the floor to engage hamstrings. Squeeze for 6s.</t>
+  </si>
+  <si>
+    <t>Lie on your stomach with a towel roll under your leg, above the knee.  Bend your knee to lift your lower leg up to 90 degrees from the floor.</t>
+  </si>
+  <si>
+    <t>12reps 1-3x per day</t>
+  </si>
+  <si>
+    <t>From standing position, bend your knee to lift your heel towrds your butt.  Find a position you can hold for 6s.</t>
+  </si>
+  <si>
+    <t>Hamstring/Quadricepts Co-contraction</t>
+  </si>
+  <si>
+    <t>Lie on your back with your leg straight. Push your heel down into the floor to contract hamstrings, then try to squeeze your quads by trying to straighten your leg.  Hold for 5s.</t>
+  </si>
+  <si>
+    <t>Straight Leg Raises</t>
+  </si>
+  <si>
+    <t>Prone Straight Leg Raises</t>
+  </si>
+  <si>
+    <t>Lie on your back with non-op leg bent 90 deg and op-leg flat against the floor with quad squeezed.  Lift the op-leg until your knee matches the height of the other knee. The goal is to keep the knee as straight as possible by keeping the quadriceps contracted.</t>
+  </si>
+  <si>
+    <t>Lie on your stomach, tighten your core and glute muscles and lift your op-leg off the table.  Lift as far as you can without rotating your hips or arching your back. Hold for 2s.</t>
+  </si>
+  <si>
+    <t>Standing Hip Extensions</t>
+  </si>
+  <si>
+    <t>Standing tall with hands supported for balance. Stand on opposite leg and extend working leg backwards at the hip. Do not let pelvis and trunk rotate. Hold end position for 2s.</t>
+  </si>
+  <si>
+    <t>Prone Hamstring Curls</t>
+  </si>
+  <si>
+    <t>Lie on your stomach and bend your knee to lift your heel towards your butt. Hold end position for 5s.</t>
+  </si>
+  <si>
+    <t>DL Heel Raise</t>
+  </si>
+  <si>
+    <t>Stand tall with feet shoulder width apart, hands on wall for support.  Lift your heels and come up on the balls of your feet.  Slow tempo.</t>
+  </si>
+  <si>
+    <t>DL Quarter Squats</t>
+  </si>
+  <si>
+    <t>Feet shoulder width apart, hands on hips, squat down about 6".  Focus is on keeping weight evenly distributed between both legs.</t>
+  </si>
+  <si>
+    <t>Side Lying Hip ADduction</t>
+  </si>
+  <si>
+    <t>Side Lying Hip ABduction</t>
+  </si>
+  <si>
+    <t>Lie on your side, bend bottom leg for support, straighten your top leg and lift it using your hip muscles</t>
+  </si>
+  <si>
+    <t>Lie on your side, straighten your bottom leg, bend top leg forward to get it out of the way.  Lift your straight bottom leg and squeeze inner thigh muscles for 2s.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -202,6 +368,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -225,9 +398,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,4 +928,417 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BBD169-EA73-8047-9513-E2AA8F61A357}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="36.6640625" customWidth="1"/>
+    <col min="5" max="5" width="99.1640625" customWidth="1"/>
+    <col min="6" max="6" width="32.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/sample_data/ACL-Protocols-Summary.xlsx
+++ b/sample_data/ACL-Protocols-Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{CC03F5E8-353A-9740-99E0-06FAF4DEB264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B4A5B8-D237-7C48-9CE0-6A23C4C854EC}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="8_{CC03F5E8-353A-9740-99E0-06FAF4DEB264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14A1068D-1C71-FA47-82B6-A13E9912DAD1}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="-18980" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{AFA84863-E3FE-B041-9D6C-E0FD21125308}"/>
+    <workbookView xWindow="2520" yWindow="-18980" windowWidth="28040" windowHeight="17440" xr2:uid="{AFA84863-E3FE-B041-9D6C-E0FD21125308}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="107">
   <si>
     <t>Melbourne</t>
   </si>
@@ -343,6 +343,21 @@
   </si>
   <si>
     <t>Lie on your side, straighten your bottom leg, bend top leg forward to get it out of the way.  Lift your straight bottom leg and squeeze inner thigh muscles for 2s.</t>
+  </si>
+  <si>
+    <t>CSI Pacific</t>
+  </si>
+  <si>
+    <t>Jumping, Landing, Running</t>
+  </si>
+  <si>
+    <t>Return to Sport</t>
+  </si>
+  <si>
+    <t>Return to Performance</t>
+  </si>
+  <si>
+    <t>Bulletproof For Life</t>
   </si>
 </sst>
 </file>
@@ -378,12 +393,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -398,10 +419,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -736,13 +759,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07B8711-A70C-A148-9538-6E7468F17D66}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="7" width="30.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -758,8 +781,11 @@
       <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -778,8 +804,11 @@
       <c r="F2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -798,8 +827,11 @@
       <c r="F3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -818,8 +850,11 @@
       <c r="F4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -838,8 +873,11 @@
       <c r="F5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -858,8 +896,11 @@
       <c r="F6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -878,8 +919,11 @@
       <c r="F7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -898,8 +942,11 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
@@ -912,8 +959,11 @@
       <c r="F9" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -923,6 +973,7 @@
       <c r="E10" t="s">
         <v>46</v>
       </c>
+      <c r="G10" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
